--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Indonesia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/TTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4094A35-0900-7246-A521-8ADB1F92E3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFEE66E-0F44-4E46-B37C-D9706D50C850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="780" windowWidth="32340" windowHeight="21360" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId21"/>
     <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId22"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3035,7 +3035,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3307,6 +3307,13 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3834,7 +3841,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3918,6 +3925,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -7537,13 +7545,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -7671,8 +7679,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7800,8 +7868,88 @@
         <f>'EV Sales Share'!AH2</f>
         <v>0.42299999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0.44146451612903093</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0.4552556451612908</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0.46904677419354712</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0.482837903225807</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0.49662903225806332</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0.51042016129032319</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0.52421129032257952</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.53800241935483939</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.55179354838709571</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.56558467741935559</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.57937580645161191</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.59316693548387178</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.6069580645161281</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.62074919354838798</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.6345403225806443</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.64833145161290417</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.6621225806451605</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.67591370967742037</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.68970483870967669</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.70349596774193657</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7929,8 +8077,88 @@
         <f>Data!AL11</f>
         <v>1.2259779596081354E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1.3765958881985091E-3</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1.4121537648702776E-3</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1.447711641542046E-3</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1.4832695182138145E-3</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1.5188273948855968E-3</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1.5543852715573653E-3</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1.5899431482291337E-3</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1.6255010249009022E-3</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1.6610589015726707E-3</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1.6966167782444391E-3</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1.7321746549162076E-3</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1.7677325315879761E-3</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1.8032904082597445E-3</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1.838848284931513E-3</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1.8744061616032814E-3</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1.9099640382750499E-3</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>1.9455219149468322E-3</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>1.9810797916186007E-3</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>2.0166376682903692E-3</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>2.0521955449621376E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8058,8 +8286,88 @@
         <f>Data!AL12</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8187,8 +8495,88 @@
         <f>Data!AL13</f>
         <v>3.0818463927506423E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>3.1705284170691295E-2</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>3.2592104413876166E-2</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>3.347892465706126E-2</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>3.4365744900246131E-2</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>3.5252565143431003E-2</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>3.6139385386615874E-2</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>3.7026205629800968E-2</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>3.7913025872985839E-2</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>3.8799846116170711E-2</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>3.9686666359355804E-2</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>4.0573486602540676E-2</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>4.1460306845725547E-2</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>4.2347127088910641E-2</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>4.3233947332095513E-2</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>4.4120767575280384E-2</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>4.5007587818465478E-2</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>4.5894408061650349E-2</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>4.6781228304835221E-2</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>4.7668048548020314E-2</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>4.8554868791205186E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8316,8 +8704,88 @@
         <f>Data!AL14</f>
         <v>0.32773377328321535</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0.39778782460026818</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0.40505317297535726</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0.41231852135044633</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0.41958386972553541</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0.42684921810062271</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0.43411456647571178</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0.44137991485080086</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0.44864526322588993</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0.45591061160097723</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0.46317595997606631</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0.47044130835115539</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0.47770665672624446</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0.48497200510133354</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0.49223735347642084</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0.49950270185150991</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0.50676805022659899</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0.51403339860168806</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0.52129874697677536</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0.52856409535186444</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0.53582944372695351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -8445,8 +8913,88 @@
         <f>Data!AL15</f>
         <v>8.6165104068937348E-4</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>8.7975251645557029E-4</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>8.9785399222177403E-4</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>9.1595546798797084E-4</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>9.3405694375416765E-4</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>9.5215841952036445E-4</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>9.7025989528656126E-4</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>9.8836137105275806E-4</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>1.0064628468189549E-3</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>1.0245643225851586E-3</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>1.0426657983513554E-3</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>1.0607672741175522E-3</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>1.078868749883749E-3</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>1.0969702256499458E-3</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>1.1150717014161426E-3</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>1.1331731771823395E-3</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>1.1512746529485432E-3</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>1.16937612871474E-3</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>1.1874776044809368E-3</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>1.2055790802471336E-3</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>1.2236805560133304E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -8573,6 +9121,86 @@
       <c r="AF8">
         <f>Data!AL16</f>
         <v>3.1168958329050089E-4</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>3.6193428069642569E-4</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>3.7379604755572587E-4</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>3.8565781441502953E-4</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>3.9751958127433318E-4</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>4.0938134813363683E-4</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>4.2124311499294048E-4</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>4.3310488185224413E-4</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>4.4496664871154779E-4</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>4.5682841557085144E-4</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>4.6869018243015162E-4</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>4.8055194928945527E-4</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>4.9241371614875892E-4</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>5.0427548300806257E-4</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>5.1613724986736623E-4</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>5.2799901672666988E-4</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>5.3986078358597353E-4</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>5.5172255044527718E-4</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>5.6358431730457736E-4</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>5.7544608416388102E-4</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
+        <v>5.8730785102318467E-4</v>
       </c>
     </row>
   </sheetData>
@@ -8585,13 +9213,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -8719,8 +9347,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8848,8 +9536,88 @@
         <f>Data!AL17</f>
         <v>0.9999999881542101</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>AF2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8977,8 +9745,88 @@
         <f>Data!AL18</f>
         <v>1.235369525889815E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1.2351562279764002E-3</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1.2349429300629856E-3</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1.2347296321495709E-3</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1.2345163342361565E-3</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1.2343030363227421E-3</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1.2340897384093275E-3</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1.2338764404959128E-3</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1.2336631425824984E-3</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1.233449844669084E-3</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1.2332365467556694E-3</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1.2330232488422547E-3</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1.2328099509288403E-3</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1.2325966530154259E-3</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1.2323833551020113E-3</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1.2321700571885966E-3</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1.2319567592751822E-3</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AH3:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1.2317434613617678E-3</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="2"/>
+        <v>1.2315301634483532E-3</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="2"/>
+        <v>1.2313168655349385E-3</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="2"/>
+        <v>1.2311035676215241E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -9106,8 +9954,88 @@
         <f>Data!AL19</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9235,8 +10163,88 @@
         <f>Data!AL20</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -9364,8 +10372,88 @@
         <f>Data!AL21</f>
         <v>0.32413298494392645</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0.38188095235825514</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0.39551409100636903</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>0.40914722965447936</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="2"/>
+        <v>0.42278036830259325</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="2"/>
+        <v>0.43641350695070358</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="2"/>
+        <v>0.45004664559881746</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="2"/>
+        <v>0.46367978424693135</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="2"/>
+        <v>0.47731292289504168</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="2"/>
+        <v>0.49094606154315557</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="2"/>
+        <v>0.50457920019126945</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="2"/>
+        <v>0.51821233883937978</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="2"/>
+        <v>0.53184547748749367</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="2"/>
+        <v>0.545478616135604</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="2"/>
+        <v>0.55911175478371788</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="2"/>
+        <v>0.57274489343183177</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="2"/>
+        <v>0.5863780320799421</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="2"/>
+        <v>0.60001117072805599</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="2"/>
+        <v>0.61364430937616987</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="2"/>
+        <v>0.6272774480242802</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="2"/>
+        <v>0.64091058667239409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -9493,8 +10581,88 @@
         <f>Data!AL22</f>
         <v>8.6165104068937001E-4</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>8.7532986991119277E-4</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="2"/>
+        <v>8.8900869913301206E-4</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="2"/>
+        <v>9.0268752835483135E-4</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="2"/>
+        <v>9.1636635757665064E-4</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="2"/>
+        <v>9.3004518679846993E-4</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="2"/>
+        <v>9.4372401602029268E-4</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="2"/>
+        <v>9.5740284524211197E-4</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="2"/>
+        <v>9.7108167446393126E-4</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="2"/>
+        <v>9.8476050368575055E-4</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="2"/>
+        <v>9.9843933290757331E-4</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="2"/>
+        <v>1.0121181621293926E-3</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="2"/>
+        <v>1.0257969913512119E-3</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="2"/>
+        <v>1.0394758205730312E-3</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="2"/>
+        <v>1.0531546497948505E-3</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="2"/>
+        <v>1.0668334790166732E-3</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="2"/>
+        <v>1.0805123082384925E-3</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="2"/>
+        <v>1.0941911374603118E-3</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="2"/>
+        <v>1.1078699666821311E-3</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="2"/>
+        <v>1.1215487959039504E-3</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="2"/>
+        <v>1.1352276251257731E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -9621,6 +10789,86 @@
       <c r="AF8">
         <f>Data!AL23</f>
         <v>3.1136358282645159E-4</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>3.6683653642968425E-4</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="2"/>
+        <v>3.7993258987632783E-4</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="2"/>
+        <v>3.9302864332297141E-4</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="2"/>
+        <v>4.0612469676961846E-4</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="2"/>
+        <v>4.1922075021626204E-4</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="2"/>
+        <v>4.3231680366290562E-4</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="2"/>
+        <v>4.4541285710955267E-4</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="2"/>
+        <v>4.5850891055619625E-4</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="2"/>
+        <v>4.7160496400283983E-4</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="2"/>
+        <v>4.8470101744948341E-4</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="2"/>
+        <v>4.9779707089613046E-4</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="2"/>
+        <v>5.1089312434277404E-4</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="2"/>
+        <v>5.2398917778941762E-4</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="2"/>
+        <v>5.3708523123606466E-4</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="2"/>
+        <v>5.5018128468270824E-4</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="2"/>
+        <v>5.6327733812935182E-4</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="2"/>
+        <v>5.763733915759954E-4</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="2"/>
+        <v>5.8946944502264245E-4</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="2"/>
+        <v>6.0256549846928603E-4</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="2"/>
+        <v>6.1566155191592961E-4</v>
       </c>
     </row>
   </sheetData>
@@ -9633,13 +10881,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -9767,8 +11015,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1" s="51">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="51">
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="51">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="51">
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="51">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="51">
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="51">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="51">
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="51">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="51">
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="51">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="51">
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="51">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="51">
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="51">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="51">
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="51">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="51">
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="51">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="51">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -9896,8 +11204,88 @@
         <f>Data!AL24</f>
         <v>0.9999999881542101</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2" s="51">
+        <f>AF2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AH2" s="51">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AI2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AJ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AK2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AL2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AM2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AN2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AO2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AP2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AQ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AR2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AS2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AT2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AU2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AV2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AW2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AX2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AY2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AZ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10025,8 +11413,68 @@
         <f>Data!AL25</f>
         <v>0.16005020400931197</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3" s="51">
+        <v>1.377E-3</v>
+      </c>
+      <c r="AH3" s="51">
+        <v>1.4120000000000001E-3</v>
+      </c>
+      <c r="AI3" s="51">
+        <v>1.4480000000000001E-3</v>
+      </c>
+      <c r="AJ3" s="51">
+        <v>1.4829999999999999E-3</v>
+      </c>
+      <c r="AK3" s="51">
+        <v>1.519E-3</v>
+      </c>
+      <c r="AL3" s="51">
+        <v>1.554E-3</v>
+      </c>
+      <c r="AM3" s="51">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="AN3" s="51">
+        <v>1.6260000000000001E-3</v>
+      </c>
+      <c r="AO3" s="51">
+        <v>1.6609999999999999E-3</v>
+      </c>
+      <c r="AP3" s="51">
+        <v>1.6969999999999999E-3</v>
+      </c>
+      <c r="AQ3" s="51">
+        <v>1.732E-3</v>
+      </c>
+      <c r="AR3" s="51">
+        <v>1.768E-3</v>
+      </c>
+      <c r="AS3" s="51">
+        <v>1.8029999999999999E-3</v>
+      </c>
+      <c r="AT3" s="51">
+        <v>1.8389999999999999E-3</v>
+      </c>
+      <c r="AU3" s="51">
+        <v>1.874E-3</v>
+      </c>
+      <c r="AV3" s="51">
+        <v>1.91E-3</v>
+      </c>
+      <c r="AW3" s="51">
+        <v>1.946E-3</v>
+      </c>
+      <c r="AX3" s="51">
+        <v>1.9810000000000001E-3</v>
+      </c>
+      <c r="AY3" s="51">
+        <v>2.0170000000000001E-3</v>
+      </c>
+      <c r="AZ3" s="51">
+        <v>2.052E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10154,8 +11602,68 @@
         <f>Data!AL26</f>
         <v>0.29946959893376196</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AH4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AI4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AJ4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AL4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AN4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AP4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AQ4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AR4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AT4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AU4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AV4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AW4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AX4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AY4" s="51">
+        <v>3</v>
+      </c>
+      <c r="AZ4" s="51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10283,8 +11791,88 @@
         <f>Data!AL27</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5" s="51">
+        <f>AF5</f>
+        <v>3</v>
+      </c>
+      <c r="AH5" s="51">
+        <f t="shared" ref="AH5:AZ5" si="1">AG5</f>
+        <v>3</v>
+      </c>
+      <c r="AI5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AK5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AL5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AM5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AN5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AO5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AP5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AQ5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AR5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AS5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AT5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AU5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AV5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AW5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AX5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AY5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="51">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10412,8 +12000,68 @@
         <f>Data!AL28</f>
         <v>8.18920096381031E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6" s="51">
+        <v>0.39778799999999997</v>
+      </c>
+      <c r="AH6" s="51">
+        <v>0.405053</v>
+      </c>
+      <c r="AI6" s="51">
+        <v>0.41231899999999999</v>
+      </c>
+      <c r="AJ6" s="51">
+        <v>0.41958400000000001</v>
+      </c>
+      <c r="AK6" s="51">
+        <v>0.42684899999999998</v>
+      </c>
+      <c r="AL6" s="51">
+        <v>0.43411499999999997</v>
+      </c>
+      <c r="AM6" s="51">
+        <v>0.44137999999999999</v>
+      </c>
+      <c r="AN6" s="51">
+        <v>0.44864500000000002</v>
+      </c>
+      <c r="AO6" s="51">
+        <v>0.45591100000000001</v>
+      </c>
+      <c r="AP6" s="51">
+        <v>0.46317599999999998</v>
+      </c>
+      <c r="AQ6" s="51">
+        <v>0.470441</v>
+      </c>
+      <c r="AR6" s="51">
+        <v>0.47770699999999999</v>
+      </c>
+      <c r="AS6" s="51">
+        <v>0.48497200000000001</v>
+      </c>
+      <c r="AT6" s="51">
+        <v>0.49223699999999998</v>
+      </c>
+      <c r="AU6" s="51">
+        <v>0.49950299999999997</v>
+      </c>
+      <c r="AV6" s="51">
+        <v>0.506768</v>
+      </c>
+      <c r="AW6" s="51">
+        <v>0.51403299999999996</v>
+      </c>
+      <c r="AX6" s="51">
+        <v>0.52129899999999996</v>
+      </c>
+      <c r="AY6" s="51">
+        <v>0.52856400000000003</v>
+      </c>
+      <c r="AZ6" s="51">
+        <v>0.535829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -10541,8 +12189,68 @@
         <f>Data!AL29</f>
         <v>0.51993486392741062</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="51">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="AH7" s="51">
+        <v>8.9800000000000004E-4</v>
+      </c>
+      <c r="AI7" s="51">
+        <v>9.1600000000000004E-4</v>
+      </c>
+      <c r="AJ7" s="51">
+        <v>9.3400000000000004E-4</v>
+      </c>
+      <c r="AK7" s="51">
+        <v>9.5200000000000005E-4</v>
+      </c>
+      <c r="AL7" s="51">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="AM7" s="51">
+        <v>9.8799999999999995E-4</v>
+      </c>
+      <c r="AN7" s="51">
+        <v>1.0059999999999999E-3</v>
+      </c>
+      <c r="AO7" s="51">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="AP7" s="51">
+        <v>1.0430000000000001E-3</v>
+      </c>
+      <c r="AQ7" s="51">
+        <v>1.0610000000000001E-3</v>
+      </c>
+      <c r="AR7" s="51">
+        <v>1.0790000000000001E-3</v>
+      </c>
+      <c r="AS7" s="51">
+        <v>1.0970000000000001E-3</v>
+      </c>
+      <c r="AT7" s="51">
+        <v>1.1150000000000001E-3</v>
+      </c>
+      <c r="AU7" s="51">
+        <v>1.1329999999999999E-3</v>
+      </c>
+      <c r="AV7" s="51">
+        <v>1.1509999999999999E-3</v>
+      </c>
+      <c r="AW7" s="51">
+        <v>1.1689999999999999E-3</v>
+      </c>
+      <c r="AX7" s="51">
+        <v>1.1869999999999999E-3</v>
+      </c>
+      <c r="AY7" s="51">
+        <v>1.206E-3</v>
+      </c>
+      <c r="AZ7" s="51">
+        <v>1.224E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -10669,6 +12377,66 @@
       <c r="AF8">
         <f>Data!AL30</f>
         <v>0.17108784051909381</v>
+      </c>
+      <c r="AG8" s="51">
+        <v>3.6200000000000002E-4</v>
+      </c>
+      <c r="AH8" s="51">
+        <v>3.7399999999999998E-4</v>
+      </c>
+      <c r="AI8" s="51">
+        <v>3.86E-4</v>
+      </c>
+      <c r="AJ8" s="51">
+        <v>3.9800000000000002E-4</v>
+      </c>
+      <c r="AK8" s="51">
+        <v>4.0900000000000002E-4</v>
+      </c>
+      <c r="AL8" s="51">
+        <v>4.2099999999999999E-4</v>
+      </c>
+      <c r="AM8" s="51">
+        <v>4.3300000000000001E-4</v>
+      </c>
+      <c r="AN8" s="51">
+        <v>4.4499999999999997E-4</v>
+      </c>
+      <c r="AO8" s="51">
+        <v>4.57E-4</v>
+      </c>
+      <c r="AP8" s="51">
+        <v>4.6900000000000002E-4</v>
+      </c>
+      <c r="AQ8" s="51">
+        <v>4.8099999999999998E-4</v>
+      </c>
+      <c r="AR8" s="51">
+        <v>4.9200000000000003E-4</v>
+      </c>
+      <c r="AS8" s="51">
+        <v>5.04E-4</v>
+      </c>
+      <c r="AT8" s="51">
+        <v>5.1599999999999997E-4</v>
+      </c>
+      <c r="AU8" s="51">
+        <v>5.2800000000000004E-4</v>
+      </c>
+      <c r="AV8" s="51">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="AW8" s="51">
+        <v>5.5199999999999997E-4</v>
+      </c>
+      <c r="AX8" s="51">
+        <v>5.6400000000000005E-4</v>
+      </c>
+      <c r="AY8" s="51">
+        <v>5.7499999999999999E-4</v>
+      </c>
+      <c r="AZ8" s="51">
+        <v>5.8699999999999996E-4</v>
       </c>
     </row>
   </sheetData>
@@ -10681,13 +12449,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -10815,8 +12583,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1" s="51">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="51">
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="51">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="51">
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="51">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="51">
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="51">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="51">
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="51">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="51">
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="51">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="51">
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="51">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="51">
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="51">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="51">
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="51">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="51">
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="51">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="51">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10944,8 +12772,88 @@
         <f>Data!AL31</f>
         <v>0.9999999881542101</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2" s="51">
+        <f>AF2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AH2" s="51">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AI2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AJ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AK2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AL2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AM2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AN2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AO2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AP2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AQ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AR2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AS2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AT2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AU2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AV2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AW2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AX2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AY2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+      <c r="AZ2" s="51">
+        <f t="shared" si="0"/>
+        <v>0.9999999881542101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11073,8 +12981,68 @@
         <f>Data!AL32</f>
         <v>5.2333311909740617E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3" s="51">
+        <v>1.377E-3</v>
+      </c>
+      <c r="AH3" s="51">
+        <v>1.4120000000000001E-3</v>
+      </c>
+      <c r="AI3" s="51">
+        <v>1.4480000000000001E-3</v>
+      </c>
+      <c r="AJ3" s="51">
+        <v>1.4829999999999999E-3</v>
+      </c>
+      <c r="AK3" s="51">
+        <v>1.519E-3</v>
+      </c>
+      <c r="AL3" s="51">
+        <v>1.554E-3</v>
+      </c>
+      <c r="AM3" s="51">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="AN3" s="51">
+        <v>1.6260000000000001E-3</v>
+      </c>
+      <c r="AO3" s="51">
+        <v>1.6609999999999999E-3</v>
+      </c>
+      <c r="AP3" s="51">
+        <v>1.6969999999999999E-3</v>
+      </c>
+      <c r="AQ3" s="51">
+        <v>1.732E-3</v>
+      </c>
+      <c r="AR3" s="51">
+        <v>1.768E-3</v>
+      </c>
+      <c r="AS3" s="51">
+        <v>1.8029999999999999E-3</v>
+      </c>
+      <c r="AT3" s="51">
+        <v>1.8389999999999999E-3</v>
+      </c>
+      <c r="AU3" s="51">
+        <v>1.874E-3</v>
+      </c>
+      <c r="AV3" s="51">
+        <v>1.91E-3</v>
+      </c>
+      <c r="AW3" s="51">
+        <v>1.946E-3</v>
+      </c>
+      <c r="AX3" s="51">
+        <v>1.9810000000000001E-3</v>
+      </c>
+      <c r="AY3" s="51">
+        <v>2.0170000000000001E-3</v>
+      </c>
+      <c r="AZ3" s="51">
+        <v>2.052E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11202,8 +13170,88 @@
         <f>Data!AL33</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4" s="51">
+        <f>AF4</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="51">
+        <f t="shared" ref="AH4:AZ4" si="1">AG4</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11331,8 +13379,88 @@
         <f>Data!AL34</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5" s="51">
+        <f>AF5</f>
+        <v>5</v>
+      </c>
+      <c r="AH5" s="51">
+        <f t="shared" ref="AH5:AZ5" si="2">AG5</f>
+        <v>5</v>
+      </c>
+      <c r="AI5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AK5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AL5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AM5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AN5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AO5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AP5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AQ5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AR5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AS5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AT5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AU5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AV5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AW5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AX5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AY5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11460,8 +13588,68 @@
         <f>Data!AL35</f>
         <v>2.7321073384308624E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6" s="51">
+        <v>0.39778799999999997</v>
+      </c>
+      <c r="AH6" s="51">
+        <v>0.405053</v>
+      </c>
+      <c r="AI6" s="51">
+        <v>0.41231899999999999</v>
+      </c>
+      <c r="AJ6" s="51">
+        <v>0.41958400000000001</v>
+      </c>
+      <c r="AK6" s="51">
+        <v>0.42684899999999998</v>
+      </c>
+      <c r="AL6" s="51">
+        <v>0.43411499999999997</v>
+      </c>
+      <c r="AM6" s="51">
+        <v>0.44137999999999999</v>
+      </c>
+      <c r="AN6" s="51">
+        <v>0.44864500000000002</v>
+      </c>
+      <c r="AO6" s="51">
+        <v>0.45591100000000001</v>
+      </c>
+      <c r="AP6" s="51">
+        <v>0.46317599999999998</v>
+      </c>
+      <c r="AQ6" s="51">
+        <v>0.470441</v>
+      </c>
+      <c r="AR6" s="51">
+        <v>0.47770699999999999</v>
+      </c>
+      <c r="AS6" s="51">
+        <v>0.48497200000000001</v>
+      </c>
+      <c r="AT6" s="51">
+        <v>0.49223699999999998</v>
+      </c>
+      <c r="AU6" s="51">
+        <v>0.49950299999999997</v>
+      </c>
+      <c r="AV6" s="51">
+        <v>0.506768</v>
+      </c>
+      <c r="AW6" s="51">
+        <v>0.51403299999999996</v>
+      </c>
+      <c r="AX6" s="51">
+        <v>0.52129899999999996</v>
+      </c>
+      <c r="AY6" s="51">
+        <v>0.52856400000000003</v>
+      </c>
+      <c r="AZ6" s="51">
+        <v>0.535829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -11589,8 +13777,68 @@
         <f>Data!AL36</f>
         <v>6.1785980743152003E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="51">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="AH7" s="51">
+        <v>8.9800000000000004E-4</v>
+      </c>
+      <c r="AI7" s="51">
+        <v>9.1600000000000004E-4</v>
+      </c>
+      <c r="AJ7" s="51">
+        <v>9.3400000000000004E-4</v>
+      </c>
+      <c r="AK7" s="51">
+        <v>9.5200000000000005E-4</v>
+      </c>
+      <c r="AL7" s="51">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="AM7" s="51">
+        <v>9.8799999999999995E-4</v>
+      </c>
+      <c r="AN7" s="51">
+        <v>1.0059999999999999E-3</v>
+      </c>
+      <c r="AO7" s="51">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="AP7" s="51">
+        <v>1.0430000000000001E-3</v>
+      </c>
+      <c r="AQ7" s="51">
+        <v>1.0610000000000001E-3</v>
+      </c>
+      <c r="AR7" s="51">
+        <v>1.0790000000000001E-3</v>
+      </c>
+      <c r="AS7" s="51">
+        <v>1.0970000000000001E-3</v>
+      </c>
+      <c r="AT7" s="51">
+        <v>1.1150000000000001E-3</v>
+      </c>
+      <c r="AU7" s="51">
+        <v>1.1329999999999999E-3</v>
+      </c>
+      <c r="AV7" s="51">
+        <v>1.1509999999999999E-3</v>
+      </c>
+      <c r="AW7" s="51">
+        <v>1.1689999999999999E-3</v>
+      </c>
+      <c r="AX7" s="51">
+        <v>1.1869999999999999E-3</v>
+      </c>
+      <c r="AY7" s="51">
+        <v>1.206E-3</v>
+      </c>
+      <c r="AZ7" s="51">
+        <v>1.224E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -11717,6 +13965,66 @@
       <c r="AF8">
         <f>Data!AL37</f>
         <v>6.0995164686396177E-3</v>
+      </c>
+      <c r="AG8" s="51">
+        <v>3.6200000000000002E-4</v>
+      </c>
+      <c r="AH8" s="51">
+        <v>3.7399999999999998E-4</v>
+      </c>
+      <c r="AI8" s="51">
+        <v>3.86E-4</v>
+      </c>
+      <c r="AJ8" s="51">
+        <v>3.9800000000000002E-4</v>
+      </c>
+      <c r="AK8" s="51">
+        <v>4.0900000000000002E-4</v>
+      </c>
+      <c r="AL8" s="51">
+        <v>4.2099999999999999E-4</v>
+      </c>
+      <c r="AM8" s="51">
+        <v>4.3300000000000001E-4</v>
+      </c>
+      <c r="AN8" s="51">
+        <v>4.4499999999999997E-4</v>
+      </c>
+      <c r="AO8" s="51">
+        <v>4.57E-4</v>
+      </c>
+      <c r="AP8" s="51">
+        <v>4.6900000000000002E-4</v>
+      </c>
+      <c r="AQ8" s="51">
+        <v>4.8099999999999998E-4</v>
+      </c>
+      <c r="AR8" s="51">
+        <v>4.9200000000000003E-4</v>
+      </c>
+      <c r="AS8" s="51">
+        <v>5.04E-4</v>
+      </c>
+      <c r="AT8" s="51">
+        <v>5.1599999999999997E-4</v>
+      </c>
+      <c r="AU8" s="51">
+        <v>5.2800000000000004E-4</v>
+      </c>
+      <c r="AV8" s="51">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="AW8" s="51">
+        <v>5.5199999999999997E-4</v>
+      </c>
+      <c r="AX8" s="51">
+        <v>5.6400000000000005E-4</v>
+      </c>
+      <c r="AY8" s="51">
+        <v>5.7499999999999999E-4</v>
+      </c>
+      <c r="AZ8" s="51">
+        <v>5.8699999999999996E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11729,13 +14037,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -11863,8 +14171,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11992,8 +14360,88 @@
         <f>Data!AL38</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12121,8 +14569,88 @@
         <f>Data!AL39</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12250,8 +14778,88 @@
         <f>Data!AL40</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12379,8 +14987,88 @@
         <f>Data!AL41</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12508,8 +15196,88 @@
         <f>Data!AL42</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -12637,8 +15405,88 @@
         <f>Data!AL43</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -12764,6 +15612,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL44</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -12777,13 +15705,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -12911,8 +15839,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13040,8 +16028,88 @@
         <f>Data!AL45</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13169,8 +16237,88 @@
         <f>Data!AL46</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13298,8 +16446,88 @@
         <f>Data!AL47</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13427,8 +16655,88 @@
         <f>Data!AL48</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13556,8 +16864,88 @@
         <f>Data!AL49</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13685,8 +17073,88 @@
         <f>Data!AL50</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -13812,6 +17280,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL51</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -13825,13 +17373,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -13959,8 +17507,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14088,8 +17696,68 @@
         <f>Data!AL52</f>
         <v>0.99727709808185716</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14217,8 +17885,88 @@
         <f>Data!AL53</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="0">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AH3:AZ8" si="1">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14346,8 +18094,88 @@
         <f>Data!AL54</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14475,8 +18303,68 @@
         <f>Data!AL55</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14604,8 +18492,88 @@
         <f>Data!AL56</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -14733,8 +18701,88 @@
         <f>Data!AL57</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -14860,6 +18908,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL58</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -14873,13 +19001,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -15007,8 +19135,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15136,8 +19324,88 @@
         <f>Data!AL59</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15265,8 +19533,88 @@
         <f>Data!AL60</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15394,8 +19742,88 @@
         <f>Data!AL61</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15523,8 +19951,88 @@
         <f>Data!AL62</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15652,8 +20160,88 @@
         <f>Data!AL63</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -15781,8 +20369,88 @@
         <f>Data!AL64</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -15908,6 +20576,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL65</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15921,13 +20669,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -16055,8 +20803,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16184,8 +20992,88 @@
         <f>Data!AL66</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16313,8 +21201,88 @@
         <f>Data!AL67</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -16442,8 +21410,88 @@
         <f>Data!AL68</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -16571,8 +21619,88 @@
         <f>Data!AL69</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16700,8 +21828,88 @@
         <f>Data!AL70</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -16829,8 +22037,88 @@
         <f>Data!AL71</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -16956,6 +22244,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL72</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -23313,13 +28681,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -23447,8 +28815,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -23576,8 +29004,88 @@
         <f>Data!AL73</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -23705,8 +29213,88 @@
         <f>Data!AL74</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -23834,8 +29422,88 @@
         <f>Data!AL75</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -23963,8 +29631,88 @@
         <f>Data!AL76</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -24092,8 +29840,88 @@
         <f>Data!AL77</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -24221,8 +30049,88 @@
         <f>Data!AL78</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -24348,6 +30256,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL79</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -24361,13 +30349,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -24495,8 +30483,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -24624,8 +30672,88 @@
         <f>Data!AL80</f>
         <v>0.99999998753074737</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>AF2</f>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0.99999998753074737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -24753,137 +30881,297 @@
         <f>Data!AL81</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AH3:AZ8" si="2">_xlfn.FORECAST.LINEAR(AW$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <f>Data!H82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <f>Data!I82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <f>Data!J82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Data!K82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>Data!L82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <f>Data!M82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <f>Data!N82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <f>Data!O82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <f>Data!P82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>Data!Q82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f>Data!R82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <f>Data!S82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <f>Data!T82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <f>Data!U82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <f>Data!V82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <f>Data!W82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <f>Data!X82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f>Data!Y82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <f>Data!Z82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <f>Data!AA82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V4">
         <f>Data!AB82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <f>Data!AC82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X4">
         <f>Data!AD82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <f>Data!AE82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z4">
         <f>Data!AF82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA4">
         <f>Data!AG82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4">
         <f>Data!AH82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>Data!AI82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD4">
         <f>Data!AJ82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE4">
         <f>Data!AK82</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <f>Data!AL82</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25011,8 +31299,88 @@
         <f>Data!AL83</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -25140,8 +31508,88 @@
         <f>Data!AL84</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -25269,8 +31717,88 @@
         <f>Data!AL85</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -25396,6 +31924,86 @@
       </c>
       <c r="AF8">
         <f>Data!AL86</f>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -25409,13 +32017,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -25543,8 +32151,68 @@
         <f>Data!AL9</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -25641,8 +32309,88 @@
       <c r="AF2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>_xlfn.FORECAST.LINEAR(AG$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ8" si="0">_xlfn.FORECAST.LINEAR(AH$1,$B2:$AF2,$B$1:$AF$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -25739,8 +32487,88 @@
       <c r="AF3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV8" si="1">_xlfn.FORECAST.LINEAR(AG$1,$B3:$AF3,$B$1:$AF$1)</f>
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -25837,8 +32665,88 @@
       <c r="AF4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25935,8 +32843,88 @@
       <c r="AF5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -26033,8 +33021,88 @@
       <c r="AF6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -26131,8 +33199,88 @@
       <c r="AF7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -26227,6 +33375,86 @@
         <v>1</v>
       </c>
       <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68790,10 +76018,10 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82" s="7" t="str">
         <f>IF(D82=E82,"n/a",IF(OR(C82="battery electric vehicle",C82="natural gas vehicle",C82="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -68801,127 +76029,127 @@
       </c>
       <c r="H82" s="22">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,I$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,J$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,K$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,L$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,M$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,N$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,O$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,P$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,Q$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,R$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,S$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,T$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,U$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,V$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,W$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,X$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,Y$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,Z$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AA$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AB$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AC$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AD$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AE$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AF$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AG$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AH$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AI$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AJ$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AK$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL82">
         <f>IF($F82="s-curve",$D82+($E82-$D82)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D82:$E82,$D$9:$E$9,AL$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.2">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Indonesia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4094A35-0900-7246-A521-8ADB1F92E3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B226CEA1-3B86-4F9F-8278-B8FFB8797916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -5001,6 +5001,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5008,7 +5009,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6719,17 +6719,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B134"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="56.33203125" customWidth="1"/>
+    <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6737,530 +6737,530 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="31"/>
     </row>
-    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="49">
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="50" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <v>2022</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="34"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>33</v>
       </c>
       <c r="B65" s="14"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B80" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>55</v>
       </c>
@@ -7278,9 +7278,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8005126-0097-8C42-9F84-7E65D20BA04B}">
   <dimension ref="A1:AH13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>920</v>
       </c>
@@ -7384,21 +7384,21 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>987</v>
       </c>
       <c r="B2">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>5.0000000000000001E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="E2">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="F2">
         <v>0.01</v>
@@ -7514,16 +7514,16 @@
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="AC11" s="44"/>
       <c r="AD11" s="44"/>
       <c r="AE11" s="44"/>
       <c r="AF11" s="44"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B12" s="44"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B13" s="44"/>
     </row>
   </sheetData>
@@ -7538,12 +7538,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -7672,17 +7672,17 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>'EV Sales Share'!D2</f>
-        <v>5.0000000000000001E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C2">
         <f>'EV Sales Share'!E2</f>
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="D2">
         <f>'EV Sales Share'!F2</f>
@@ -7801,7 +7801,7 @@
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7930,7 +7930,7 @@
         <v>1.2259779596081354E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8059,7 +8059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>3.0818463927506423E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>0.32773377328321535</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>8.6165104068937348E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -8586,12 +8586,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>0.9999999881542101</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>1.235369525889815E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>0.32413298494392645</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>8.6165104068937001E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -9634,12 +9634,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>0.9999999881542101</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10026,7 +10026,7 @@
         <v>0.16005020400931197</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>0.29946959893376196</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>8.18920096381031E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>0.51993486392741062</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -10682,12 +10682,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>0.9999999881542101</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11074,7 +11074,7 @@
         <v>5.2333311909740617E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11203,7 +11203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11332,7 +11332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>2.7321073384308624E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -11590,7 +11590,7 @@
         <v>6.1785980743152003E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -11730,12 +11730,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -11864,7 +11864,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11993,7 +11993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -12638,7 +12638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -12778,12 +12778,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13170,7 +13170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13557,7 +13557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13686,7 +13686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -13826,12 +13826,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -13960,7 +13960,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>0.99727709808185716</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14605,7 +14605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -14734,7 +14734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -14874,12 +14874,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -15008,7 +15008,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15524,7 +15524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -15922,12 +15922,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16185,7 +16185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16314,7 +16314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -16572,7 +16572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -16967,9 +16967,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="E1">
         <v>2020</v>
       </c>
@@ -17067,27 +17067,27 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>147</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -17210,7 +17210,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -17430,7 +17430,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -17540,7 +17540,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>165</v>
       </c>
@@ -17548,7 +17548,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>167</v>
       </c>
@@ -17658,7 +17658,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -17768,7 +17768,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
@@ -17878,7 +17878,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>176</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>179</v>
       </c>
@@ -18098,7 +18098,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>182</v>
       </c>
@@ -18208,7 +18208,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>185</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>188</v>
       </c>
@@ -18428,7 +18428,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>191</v>
       </c>
@@ -18538,7 +18538,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>194</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>200</v>
       </c>
@@ -18868,7 +18868,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -18978,7 +18978,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>205</v>
       </c>
@@ -19088,7 +19088,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -19198,7 +19198,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -19308,7 +19308,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>216</v>
       </c>
@@ -19426,7 +19426,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>218</v>
       </c>
@@ -19434,7 +19434,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>155</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>159</v>
       </c>
@@ -19654,7 +19654,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>224</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>227</v>
       </c>
@@ -19772,7 +19772,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>167</v>
       </c>
@@ -19882,7 +19882,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>170</v>
       </c>
@@ -19992,7 +19992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>173</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>176</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>179</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>182</v>
       </c>
@@ -20432,7 +20432,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>185</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>188</v>
       </c>
@@ -20652,7 +20652,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>191</v>
       </c>
@@ -20762,7 +20762,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>194</v>
       </c>
@@ -20872,7 +20872,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>197</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>200</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>202</v>
       </c>
@@ -21202,7 +21202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>205</v>
       </c>
@@ -21312,7 +21312,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>257</v>
       </c>
@@ -21422,7 +21422,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>115</v>
       </c>
@@ -21532,7 +21532,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>117</v>
       </c>
@@ -21752,7 +21752,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -21862,7 +21862,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>270</v>
       </c>
@@ -21983,7 +21983,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>273</v>
       </c>
@@ -22093,7 +22093,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>276</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>279</v>
       </c>
@@ -22313,7 +22313,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>282</v>
       </c>
@@ -22423,7 +22423,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>285</v>
       </c>
@@ -22533,7 +22533,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>288</v>
       </c>
@@ -22643,7 +22643,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -22753,7 +22753,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>294</v>
       </c>
@@ -22863,7 +22863,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>120</v>
       </c>
@@ -22973,7 +22973,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>299</v>
       </c>
@@ -23083,7 +23083,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>302</v>
       </c>
@@ -23193,7 +23193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>121</v>
       </c>
@@ -23314,12 +23314,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -23448,7 +23448,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -23577,7 +23577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -23706,7 +23706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -23835,7 +23835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -23964,7 +23964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -24093,7 +24093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -24362,12 +24362,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -24496,7 +24496,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -24506,126 +24506,126 @@
       </c>
       <c r="C2">
         <f>Data!I80</f>
-        <v>0.10909682119561298</v>
+        <v>1.4774031693273055E-2</v>
       </c>
       <c r="D2">
         <f>Data!J80</f>
-        <v>0.19781611144141825</v>
+        <v>1.984030573407751E-2</v>
       </c>
       <c r="E2">
         <f>Data!K80</f>
-        <v>0.33181222783183389</v>
+        <v>2.6596993576865863E-2</v>
       </c>
       <c r="F2">
         <f>Data!L80</f>
-        <v>0.5</v>
+        <v>3.5571189272636181E-2</v>
       </c>
       <c r="G2">
         <f>Data!M80</f>
-        <v>0.66818777216816616</v>
+        <v>4.7425873177566781E-2</v>
       </c>
       <c r="H2">
         <f>Data!N80</f>
-        <v>0.80218388855858169</v>
+        <v>6.2973356056996513E-2</v>
       </c>
       <c r="I2">
         <f>Data!O80</f>
-        <v>0.89090317880438707</v>
+        <v>8.317269649392238E-2</v>
       </c>
       <c r="J2">
         <f>Data!P80</f>
-        <v>0.94267582410113127</v>
+        <v>0.10909682119561293</v>
       </c>
       <c r="K2">
         <f>Data!Q80</f>
-        <v>0.97068776924864364</v>
+        <v>0.14185106490048782</v>
       </c>
       <c r="L2">
         <f>Data!R80</f>
-        <v>0.98522596830672693</v>
+        <v>0.18242552380635635</v>
       </c>
       <c r="M2">
         <f>Data!S80</f>
-        <v>0.99260845865571812</v>
+        <v>0.23147521650098238</v>
       </c>
       <c r="N2">
         <f>Data!T80</f>
-        <v>0.99631576010056411</v>
+        <v>0.28905049737499605</v>
       </c>
       <c r="O2">
         <f>Data!U80</f>
-        <v>0.99816706105750719</v>
+        <v>0.35434369377420455</v>
       </c>
       <c r="P2">
         <f>Data!V80</f>
-        <v>0.9990889488055994</v>
+        <v>0.42555748318834102</v>
       </c>
       <c r="Q2">
         <f>Data!W80</f>
-        <v>0.9995473777767595</v>
+        <v>0.5</v>
       </c>
       <c r="R2">
         <f>Data!X80</f>
-        <v>0.99977518322976666</v>
+        <v>0.57444251681165903</v>
       </c>
       <c r="S2">
         <f>Data!Y80</f>
-        <v>0.99988834665937043</v>
+        <v>0.6456563062257954</v>
       </c>
       <c r="T2">
         <f>Data!Z80</f>
-        <v>0.99994455147527717</v>
+        <v>0.71094950262500389</v>
       </c>
       <c r="U2">
         <f>Data!AA80</f>
-        <v>0.99997246430888531</v>
+        <v>0.76852478349901754</v>
       </c>
       <c r="V2">
         <f>Data!AB80</f>
-        <v>0.99998632599091541</v>
+        <v>0.81757447619364365</v>
       </c>
       <c r="W2">
         <f>Data!AC80</f>
-        <v>0.99999320964130201</v>
+        <v>0.85814893509951229</v>
       </c>
       <c r="X2">
         <f>Data!AD80</f>
-        <v>0.99999662799613631</v>
+        <v>0.89090317880438707</v>
       </c>
       <c r="Y2">
         <f>Data!AE80</f>
-        <v>0.99999832550959444</v>
+        <v>0.91682730350607766</v>
       </c>
       <c r="Z2">
         <f>Data!AF80</f>
-        <v>0.99999916847197223</v>
+        <v>0.9370266439430035</v>
       </c>
       <c r="AA2">
         <f>Data!AG80</f>
-        <v>0.99999958707522896</v>
+        <v>0.95257412682243336</v>
       </c>
       <c r="AB2">
         <f>Data!AH80</f>
-        <v>0.99999979494758462</v>
+        <v>0.96442881072736386</v>
       </c>
       <c r="AC2">
         <f>Data!AI80</f>
-        <v>0.99999989817397339</v>
+        <v>0.97340300642313404</v>
       </c>
       <c r="AD2">
         <f>Data!AJ80</f>
-        <v>0.99999994943468906</v>
+        <v>0.98015969426592253</v>
       </c>
       <c r="AE2">
         <f>Data!AK80</f>
-        <v>0.99999997489000902</v>
+        <v>0.98522596830672693</v>
       </c>
       <c r="AF2">
         <f>Data!AL80</f>
         <v>0.99999998753074737</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -24754,7 +24754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -24883,7 +24883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25012,7 +25012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -25141,7 +25141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -25270,7 +25270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -25410,12 +25410,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -25544,7 +25544,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -25642,7 +25642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -25838,7 +25838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25936,7 +25936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -26034,7 +26034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -26238,9 +26238,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
         <v>2020</v>
       </c>
@@ -26338,27 +26338,27 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>147</v>
       </c>
@@ -26465,7 +26465,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>310</v>
       </c>
@@ -26473,7 +26473,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -26481,7 +26481,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -26591,7 +26591,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -26701,7 +26701,7 @@
         <v>-0.115</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -26811,7 +26811,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>165</v>
       </c>
@@ -26819,7 +26819,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>167</v>
       </c>
@@ -26929,7 +26929,7 @@
         <v>-3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -27039,7 +27039,7 @@
         <v>-3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
@@ -27149,7 +27149,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>176</v>
       </c>
@@ -27259,7 +27259,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>179</v>
       </c>
@@ -27369,7 +27369,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>182</v>
       </c>
@@ -27479,7 +27479,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>185</v>
       </c>
@@ -27589,7 +27589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>188</v>
       </c>
@@ -27699,7 +27699,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>191</v>
       </c>
@@ -27809,7 +27809,7 @@
         <v>-2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>194</v>
       </c>
@@ -27919,7 +27919,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -28029,7 +28029,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>200</v>
       </c>
@@ -28139,7 +28139,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -28249,7 +28249,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>205</v>
       </c>
@@ -28359,7 +28359,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -28469,7 +28469,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -28579,7 +28579,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>330</v>
       </c>
@@ -28587,7 +28587,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>218</v>
       </c>
@@ -28595,7 +28595,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -28705,7 +28705,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>159</v>
       </c>
@@ -28815,7 +28815,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>224</v>
       </c>
@@ -28925,7 +28925,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>227</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -29043,7 +29043,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>170</v>
       </c>
@@ -29153,7 +29153,7 @@
         <v>-0.11600000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>173</v>
       </c>
@@ -29263,7 +29263,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>176</v>
       </c>
@@ -29373,7 +29373,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>179</v>
       </c>
@@ -29483,7 +29483,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>182</v>
       </c>
@@ -29593,7 +29593,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>185</v>
       </c>
@@ -29703,7 +29703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -29813,7 +29813,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -29923,7 +29923,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>194</v>
       </c>
@@ -30033,7 +30033,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>197</v>
       </c>
@@ -30143,7 +30143,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>200</v>
       </c>
@@ -30253,7 +30253,7 @@
         <v>-2.7E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>202</v>
       </c>
@@ -30363,7 +30363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>205</v>
       </c>
@@ -30473,7 +30473,7 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>257</v>
       </c>
@@ -30583,7 +30583,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -30693,7 +30693,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -30812,29 +30812,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E495E93-490C-4630-BB04-9B57B46A213E}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>920</v>
       </c>
@@ -30869,7 +30869,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2050</v>
       </c>
@@ -30904,7 +30904,7 @@
         <v>968.61480700000004</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2049</v>
       </c>
@@ -30939,7 +30939,7 @@
         <v>975.68035899999995</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2048</v>
       </c>
@@ -30974,7 +30974,7 @@
         <v>981.37280299999998</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2047</v>
       </c>
@@ -31009,7 +31009,7 @@
         <v>975.81964100000005</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2046</v>
       </c>
@@ -31044,7 +31044,7 @@
         <v>980.589966</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2045</v>
       </c>
@@ -31079,7 +31079,7 @@
         <v>984.091858</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2044</v>
       </c>
@@ -31114,7 +31114,7 @@
         <v>976.13824499999998</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2043</v>
       </c>
@@ -31149,7 +31149,7 @@
         <v>977.10333300000002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2042</v>
       </c>
@@ -31184,7 +31184,7 @@
         <v>979.39685099999997</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2041</v>
       </c>
@@ -31219,7 +31219,7 @@
         <v>979.05828899999995</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2040</v>
       </c>
@@ -31254,7 +31254,7 @@
         <v>979.86975099999995</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -31289,7 +31289,7 @@
         <v>981.14685099999997</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2038</v>
       </c>
@@ -31324,7 +31324,7 @@
         <v>979.91186500000003</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2037</v>
       </c>
@@ -31359,7 +31359,7 @@
         <v>977.93768299999999</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2036</v>
       </c>
@@ -31394,7 +31394,7 @@
         <v>982.68225099999995</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2035</v>
       </c>
@@ -31429,7 +31429,7 @@
         <v>985.55090299999995</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2034</v>
       </c>
@@ -31464,7 +31464,7 @@
         <v>980.60241699999995</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2033</v>
       </c>
@@ -31499,7 +31499,7 @@
         <v>977.975098</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -31534,7 +31534,7 @@
         <v>975.89404300000001</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2031</v>
       </c>
@@ -31569,7 +31569,7 @@
         <v>972.47125200000005</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2030</v>
       </c>
@@ -31604,7 +31604,7 @@
         <v>970.98468000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2029</v>
       </c>
@@ -31639,7 +31639,7 @@
         <v>981.23956299999998</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2028</v>
       </c>
@@ -31674,7 +31674,7 @@
         <v>966.18756099999996</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2027</v>
       </c>
@@ -31709,7 +31709,7 @@
         <v>953.71936000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2026</v>
       </c>
@@ -31744,7 +31744,7 @@
         <v>966.38690199999996</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2025</v>
       </c>
@@ -31779,7 +31779,7 @@
         <v>964.77038600000003</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2024</v>
       </c>
@@ -31814,7 +31814,7 @@
         <v>940.58337400000005</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2023</v>
       </c>
@@ -31849,7 +31849,7 @@
         <v>906.911743</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2022</v>
       </c>
@@ -31884,7 +31884,7 @@
         <v>878.96453899999995</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -31919,7 +31919,7 @@
         <v>822.79125999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2020</v>
       </c>
@@ -31954,7 +31954,7 @@
         <v>728.74066200000004</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2019</v>
       </c>
@@ -31967,9 +31967,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ262"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
         <v>2020</v>
       </c>
@@ -32067,27 +32067,27 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>147</v>
       </c>
@@ -32194,7 +32194,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -32202,7 +32202,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>400</v>
       </c>
@@ -32210,7 +32210,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>401</v>
       </c>
@@ -32218,7 +32218,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>402</v>
       </c>
@@ -32328,7 +32328,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>404</v>
       </c>
@@ -32438,7 +32438,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>406</v>
       </c>
@@ -32548,7 +32548,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>408</v>
       </c>
@@ -32658,7 +32658,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>410</v>
       </c>
@@ -32768,7 +32768,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>282</v>
       </c>
@@ -32878,7 +32878,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>413</v>
       </c>
@@ -32988,7 +32988,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>415</v>
       </c>
@@ -33098,7 +33098,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>294</v>
       </c>
@@ -33208,7 +33208,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>418</v>
       </c>
@@ -33318,7 +33318,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>420</v>
       </c>
@@ -33326,7 +33326,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>402</v>
       </c>
@@ -33436,7 +33436,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>404</v>
       </c>
@@ -33546,7 +33546,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>406</v>
       </c>
@@ -33656,7 +33656,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>408</v>
       </c>
@@ -33766,7 +33766,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>410</v>
       </c>
@@ -33876,7 +33876,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -33986,7 +33986,7 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>413</v>
       </c>
@@ -34096,7 +34096,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>415</v>
       </c>
@@ -34206,7 +34206,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>294</v>
       </c>
@@ -34316,7 +34316,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>430</v>
       </c>
@@ -34426,7 +34426,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>432</v>
       </c>
@@ -34434,7 +34434,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>402</v>
       </c>
@@ -34544,7 +34544,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>404</v>
       </c>
@@ -34654,7 +34654,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>406</v>
       </c>
@@ -34764,7 +34764,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>408</v>
       </c>
@@ -34874,7 +34874,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>410</v>
       </c>
@@ -34984,7 +34984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>282</v>
       </c>
@@ -35094,7 +35094,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>413</v>
       </c>
@@ -35204,7 +35204,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>415</v>
       </c>
@@ -35314,7 +35314,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>294</v>
       </c>
@@ -35424,7 +35424,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>442</v>
       </c>
@@ -35534,7 +35534,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>444</v>
       </c>
@@ -35644,7 +35644,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>446</v>
       </c>
@@ -35652,7 +35652,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>401</v>
       </c>
@@ -35660,7 +35660,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>402</v>
       </c>
@@ -35770,7 +35770,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>404</v>
       </c>
@@ -35880,7 +35880,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>406</v>
       </c>
@@ -35990,7 +35990,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>408</v>
       </c>
@@ -36100,7 +36100,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>410</v>
       </c>
@@ -36210,7 +36210,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>282</v>
       </c>
@@ -36320,7 +36320,7 @@
         <v>0.13200000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>413</v>
       </c>
@@ -36430,7 +36430,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>415</v>
       </c>
@@ -36540,7 +36540,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>294</v>
       </c>
@@ -36650,7 +36650,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>418</v>
       </c>
@@ -36760,7 +36760,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>420</v>
       </c>
@@ -36768,7 +36768,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>402</v>
       </c>
@@ -36878,7 +36878,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>404</v>
       </c>
@@ -36988,7 +36988,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>406</v>
       </c>
@@ -37098,7 +37098,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>408</v>
       </c>
@@ -37208,7 +37208,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>410</v>
       </c>
@@ -37318,7 +37318,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>282</v>
       </c>
@@ -37428,7 +37428,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>413</v>
       </c>
@@ -37538,7 +37538,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>415</v>
       </c>
@@ -37648,7 +37648,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>294</v>
       </c>
@@ -37758,7 +37758,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>430</v>
       </c>
@@ -37868,7 +37868,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>432</v>
       </c>
@@ -37876,7 +37876,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>402</v>
       </c>
@@ -37986,7 +37986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>404</v>
       </c>
@@ -38096,7 +38096,7 @@
         <v>-2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>406</v>
       </c>
@@ -38206,7 +38206,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>408</v>
       </c>
@@ -38316,7 +38316,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>410</v>
       </c>
@@ -38426,7 +38426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>282</v>
       </c>
@@ -38536,7 +38536,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>413</v>
       </c>
@@ -38646,7 +38646,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>415</v>
       </c>
@@ -38756,7 +38756,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>294</v>
       </c>
@@ -38866,7 +38866,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>442</v>
       </c>
@@ -38976,7 +38976,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>401</v>
       </c>
@@ -38987,7 +38987,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>402</v>
       </c>
@@ -39097,7 +39097,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>404</v>
       </c>
@@ -39207,7 +39207,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>406</v>
       </c>
@@ -39317,7 +39317,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>408</v>
       </c>
@@ -39427,7 +39427,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>410</v>
       </c>
@@ -39537,7 +39537,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>282</v>
       </c>
@@ -39647,7 +39647,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>413</v>
       </c>
@@ -39757,7 +39757,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>415</v>
       </c>
@@ -39867,7 +39867,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>294</v>
       </c>
@@ -39977,7 +39977,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>487</v>
       </c>
@@ -40087,7 +40087,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>489</v>
       </c>
@@ -40095,7 +40095,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="98" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>401</v>
       </c>
@@ -40103,7 +40103,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>402</v>
       </c>
@@ -40213,7 +40213,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>404</v>
       </c>
@@ -40323,7 +40323,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>406</v>
       </c>
@@ -40433,7 +40433,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>408</v>
       </c>
@@ -40543,7 +40543,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>410</v>
       </c>
@@ -40653,7 +40653,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>282</v>
       </c>
@@ -40763,7 +40763,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>413</v>
       </c>
@@ -40873,7 +40873,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>415</v>
       </c>
@@ -40983,7 +40983,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>294</v>
       </c>
@@ -41093,7 +41093,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>499</v>
       </c>
@@ -41200,7 +41200,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>420</v>
       </c>
@@ -41208,7 +41208,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>402</v>
       </c>
@@ -41318,7 +41318,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>404</v>
       </c>
@@ -41428,7 +41428,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>406</v>
       </c>
@@ -41538,7 +41538,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>408</v>
       </c>
@@ -41648,7 +41648,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>410</v>
       </c>
@@ -41758,7 +41758,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>282</v>
       </c>
@@ -41868,7 +41868,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>413</v>
       </c>
@@ -41978,7 +41978,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>415</v>
       </c>
@@ -42088,7 +42088,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>294</v>
       </c>
@@ -42198,7 +42198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>510</v>
       </c>
@@ -42305,7 +42305,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>432</v>
       </c>
@@ -42313,7 +42313,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>402</v>
       </c>
@@ -42423,7 +42423,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>404</v>
       </c>
@@ -42533,7 +42533,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>406</v>
       </c>
@@ -42643,7 +42643,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>408</v>
       </c>
@@ -42753,7 +42753,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>410</v>
       </c>
@@ -42863,7 +42863,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>282</v>
       </c>
@@ -42973,7 +42973,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>413</v>
       </c>
@@ -43083,7 +43083,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>415</v>
       </c>
@@ -43193,7 +43193,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>294</v>
       </c>
@@ -43303,7 +43303,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>521</v>
       </c>
@@ -43410,7 +43410,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>523</v>
       </c>
@@ -43517,7 +43517,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>525</v>
       </c>
@@ -43525,7 +43525,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>401</v>
       </c>
@@ -43533,7 +43533,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>402</v>
       </c>
@@ -43643,7 +43643,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>404</v>
       </c>
@@ -43753,7 +43753,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>406</v>
       </c>
@@ -43863,7 +43863,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -43973,7 +43973,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>410</v>
       </c>
@@ -44083,7 +44083,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>282</v>
       </c>
@@ -44193,7 +44193,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>413</v>
       </c>
@@ -44303,7 +44303,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>415</v>
       </c>
@@ -44413,7 +44413,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>294</v>
       </c>
@@ -44523,7 +44523,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>418</v>
       </c>
@@ -44633,7 +44633,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>420</v>
       </c>
@@ -44641,7 +44641,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="145" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>402</v>
       </c>
@@ -44751,7 +44751,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>404</v>
       </c>
@@ -44861,7 +44861,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>406</v>
       </c>
@@ -44971,7 +44971,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>408</v>
       </c>
@@ -45081,7 +45081,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>410</v>
       </c>
@@ -45191,7 +45191,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>282</v>
       </c>
@@ -45301,7 +45301,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>413</v>
       </c>
@@ -45411,7 +45411,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="152" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>415</v>
       </c>
@@ -45521,7 +45521,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="153" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -45631,7 +45631,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="154" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>430</v>
       </c>
@@ -45741,7 +45741,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>432</v>
       </c>
@@ -45749,7 +45749,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="156" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>402</v>
       </c>
@@ -45859,7 +45859,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>404</v>
       </c>
@@ -45969,7 +45969,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>406</v>
       </c>
@@ -46079,7 +46079,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="159" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>408</v>
       </c>
@@ -46189,7 +46189,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>410</v>
       </c>
@@ -46299,7 +46299,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>282</v>
       </c>
@@ -46409,7 +46409,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>413</v>
       </c>
@@ -46519,7 +46519,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="163" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>415</v>
       </c>
@@ -46629,7 +46629,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="164" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>294</v>
       </c>
@@ -46739,7 +46739,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="165" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>442</v>
       </c>
@@ -46849,7 +46849,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>21</v>
       </c>
@@ -46959,7 +46959,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -46967,7 +46967,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="168" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>489</v>
       </c>
@@ -46975,7 +46975,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="169" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>401</v>
       </c>
@@ -46983,7 +46983,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="170" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -47093,7 +47093,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>404</v>
       </c>
@@ -47203,7 +47203,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>406</v>
       </c>
@@ -47313,7 +47313,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>408</v>
       </c>
@@ -47423,7 +47423,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>410</v>
       </c>
@@ -47533,7 +47533,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>282</v>
       </c>
@@ -47643,7 +47643,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>413</v>
       </c>
@@ -47753,7 +47753,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>415</v>
       </c>
@@ -47863,7 +47863,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>294</v>
       </c>
@@ -47973,7 +47973,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>499</v>
       </c>
@@ -48080,7 +48080,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>420</v>
       </c>
@@ -48088,7 +48088,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>402</v>
       </c>
@@ -48198,7 +48198,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>404</v>
       </c>
@@ -48308,7 +48308,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>406</v>
       </c>
@@ -48418,7 +48418,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>408</v>
       </c>
@@ -48528,7 +48528,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>410</v>
       </c>
@@ -48638,7 +48638,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>282</v>
       </c>
@@ -48748,7 +48748,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>413</v>
       </c>
@@ -48858,7 +48858,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>415</v>
       </c>
@@ -48968,7 +48968,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>294</v>
       </c>
@@ -49078,7 +49078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>510</v>
       </c>
@@ -49185,7 +49185,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>432</v>
       </c>
@@ -49193,7 +49193,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>402</v>
       </c>
@@ -49303,7 +49303,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>404</v>
       </c>
@@ -49413,7 +49413,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>406</v>
       </c>
@@ -49523,7 +49523,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>408</v>
       </c>
@@ -49633,7 +49633,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>410</v>
       </c>
@@ -49743,7 +49743,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>282</v>
       </c>
@@ -49853,7 +49853,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>413</v>
       </c>
@@ -49963,7 +49963,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="199" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>415</v>
       </c>
@@ -50073,7 +50073,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>294</v>
       </c>
@@ -50183,7 +50183,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>521</v>
       </c>
@@ -50290,7 +50290,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>523</v>
       </c>
@@ -50397,7 +50397,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>588</v>
       </c>
@@ -50405,7 +50405,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="204" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>401</v>
       </c>
@@ -50413,7 +50413,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="205" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>402</v>
       </c>
@@ -50523,7 +50523,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>404</v>
       </c>
@@ -50633,7 +50633,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>406</v>
       </c>
@@ -50743,7 +50743,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>408</v>
       </c>
@@ -50853,7 +50853,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>410</v>
       </c>
@@ -50963,7 +50963,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>282</v>
       </c>
@@ -51073,7 +51073,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>413</v>
       </c>
@@ -51183,7 +51183,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>415</v>
       </c>
@@ -51293,7 +51293,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>294</v>
       </c>
@@ -51403,7 +51403,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>418</v>
       </c>
@@ -51513,7 +51513,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>420</v>
       </c>
@@ -51521,7 +51521,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="216" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>402</v>
       </c>
@@ -51631,7 +51631,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>404</v>
       </c>
@@ -51741,7 +51741,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>406</v>
       </c>
@@ -51851,7 +51851,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="219" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>408</v>
       </c>
@@ -51961,7 +51961,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>410</v>
       </c>
@@ -52071,7 +52071,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>282</v>
       </c>
@@ -52181,7 +52181,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="222" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>413</v>
       </c>
@@ -52291,7 +52291,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="223" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>415</v>
       </c>
@@ -52401,7 +52401,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="224" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>294</v>
       </c>
@@ -52511,7 +52511,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="225" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>430</v>
       </c>
@@ -52621,7 +52621,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>432</v>
       </c>
@@ -52629,7 +52629,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="227" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>402</v>
       </c>
@@ -52739,7 +52739,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>404</v>
       </c>
@@ -52849,7 +52849,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>406</v>
       </c>
@@ -52959,7 +52959,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="230" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>408</v>
       </c>
@@ -53069,7 +53069,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>410</v>
       </c>
@@ -53179,7 +53179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>282</v>
       </c>
@@ -53289,7 +53289,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>413</v>
       </c>
@@ -53399,7 +53399,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>415</v>
       </c>
@@ -53509,7 +53509,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>294</v>
       </c>
@@ -53619,7 +53619,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>442</v>
       </c>
@@ -53729,7 +53729,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="237" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>270</v>
       </c>
@@ -53839,7 +53839,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>39</v>
       </c>
@@ -53847,7 +53847,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="239" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>620</v>
       </c>
@@ -53957,7 +53957,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>622</v>
       </c>
@@ -54067,7 +54067,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>624</v>
       </c>
@@ -54075,7 +54075,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="242" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>625</v>
       </c>
@@ -54185,7 +54185,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>627</v>
       </c>
@@ -54295,7 +54295,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>629</v>
       </c>
@@ -54405,7 +54405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="245" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>631</v>
       </c>
@@ -54515,7 +54515,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="246" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>38</v>
       </c>
@@ -54523,7 +54523,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="247" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>633</v>
       </c>
@@ -54633,7 +54633,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>622</v>
       </c>
@@ -54743,7 +54743,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="249" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>624</v>
       </c>
@@ -54751,7 +54751,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="250" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>625</v>
       </c>
@@ -54861,7 +54861,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>627</v>
       </c>
@@ -54971,7 +54971,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>629</v>
       </c>
@@ -55081,7 +55081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>631</v>
       </c>
@@ -55191,7 +55191,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>37</v>
       </c>
@@ -55199,7 +55199,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="255" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>640</v>
       </c>
@@ -55309,7 +55309,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="256" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>642</v>
       </c>
@@ -55419,7 +55419,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>644</v>
       </c>
@@ -55529,7 +55529,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>624</v>
       </c>
@@ -55537,7 +55537,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="259" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>625</v>
       </c>
@@ -55647,7 +55647,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="260" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>627</v>
       </c>
@@ -55757,7 +55757,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>629</v>
       </c>
@@ -55867,7 +55867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>631</v>
       </c>
@@ -55986,18 +55986,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
-    <col min="6" max="8" width="23.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>128</v>
       </c>
@@ -56023,7 +56023,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -56050,7 +56050,7 @@
       </c>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -56078,7 +56078,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="24"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -56104,7 +56104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -56130,7 +56130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -56156,7 +56156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -56182,7 +56182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -56199,19 +56199,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
-    <col min="6" max="8" width="23.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>128</v>
       </c>
@@ -56237,7 +56237,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -56265,7 +56265,7 @@
       <c r="I2" s="24"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -56292,7 +56292,7 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -56318,7 +56318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -56344,7 +56344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -56370,7 +56370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -56404,81 +56404,81 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AF118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>64</v>
       </c>
       <c r="N15" s="38"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>89</v>
       </c>
       <c r="N16" s="40"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>90</v>
       </c>
@@ -56487,13 +56487,13 @@
       <c r="P17" s="41"/>
       <c r="Q17" s="41"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N18" s="41"/>
       <c r="O18" s="42"/>
       <c r="P18" s="42"/>
       <c r="Q18" s="42"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -56502,7 +56502,7 @@
       <c r="P19" s="42"/>
       <c r="Q19" s="42"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -56511,7 +56511,7 @@
       <c r="P20" s="42"/>
       <c r="Q20" s="42"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -56520,7 +56520,7 @@
       <c r="P21" s="42"/>
       <c r="Q21" s="42"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -56529,7 +56529,7 @@
       <c r="P22" s="42"/>
       <c r="Q22" s="42"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -56538,7 +56538,7 @@
       <c r="P23" s="42"/>
       <c r="Q23" s="42"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>96</v>
       </c>
@@ -56547,7 +56547,7 @@
       <c r="P24" s="42"/>
       <c r="Q24" s="42"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -56556,13 +56556,13 @@
       <c r="P25" s="42"/>
       <c r="Q25" s="42"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N26" s="41"/>
       <c r="O26" s="43"/>
       <c r="P26" s="42"/>
       <c r="Q26" s="42"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>945</v>
       </c>
@@ -56571,96 +56571,96 @@
       <c r="P27" s="42"/>
       <c r="Q27" s="42"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="N28" s="41"/>
       <c r="O28" s="43"/>
       <c r="P28" s="42"/>
       <c r="Q28" s="42"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="N29" s="41"/>
       <c r="O29" s="43"/>
       <c r="P29" s="42"/>
       <c r="Q29" s="42"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="N30" s="41"/>
       <c r="O30" s="43"/>
       <c r="P30" s="42"/>
       <c r="Q30" s="42"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="N31" s="41"/>
       <c r="O31" s="43"/>
       <c r="P31" s="42"/>
       <c r="Q31" s="42"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="N32" s="41"/>
       <c r="O32" s="43"/>
       <c r="P32" s="42"/>
       <c r="Q32" s="42"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="N33" s="41"/>
       <c r="O33" s="43"/>
       <c r="P33" s="42"/>
       <c r="Q33" s="42"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="N34" s="41"/>
       <c r="O34" s="43"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="42"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="N35" s="41"/>
       <c r="O35" s="43"/>
       <c r="P35" s="42"/>
       <c r="Q35" s="42"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="N36" s="41"/>
       <c r="O36" s="43"/>
       <c r="P36" s="42"/>
       <c r="Q36" s="42"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="N37" s="41"/>
       <c r="O37" s="43"/>
       <c r="P37" s="42"/>
       <c r="Q37" s="42"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="N38" s="41"/>
       <c r="O38" s="43"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="42"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N39" s="41"/>
       <c r="O39" s="43"/>
       <c r="P39" s="42"/>
       <c r="Q39" s="42"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N40" s="41"/>
       <c r="O40" s="43"/>
       <c r="P40" s="42"/>
       <c r="Q40" s="42"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>946</v>
       </c>
@@ -56669,7 +56669,7 @@
       <c r="P41" s="42"/>
       <c r="Q41" s="42"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>947</v>
       </c>
@@ -56678,7 +56678,7 @@
       <c r="P42" s="42"/>
       <c r="Q42" s="42"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>948</v>
       </c>
@@ -56687,13 +56687,13 @@
       <c r="P43" s="42"/>
       <c r="Q43" s="42"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N44" s="41"/>
       <c r="O44" s="43"/>
       <c r="P44" s="42"/>
       <c r="Q44" s="42"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
         <v>939</v>
       </c>
@@ -56705,7 +56705,7 @@
       <c r="P45" s="42"/>
       <c r="Q45" s="42"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="40" t="s">
         <v>940</v>
       </c>
@@ -56723,7 +56723,7 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="42"/>
     </row>
-    <row r="47" spans="1:17" ht="61" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A47" s="37" t="s">
         <v>941</v>
       </c>
@@ -56746,7 +56746,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>2010</v>
       </c>
@@ -56771,7 +56771,7 @@
         <v>2.9920693520220819E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="41">
         <v>2011</v>
       </c>
@@ -56796,7 +56796,7 @@
         <v>1.1079306479779186E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>2012</v>
       </c>
@@ -56810,7 +56810,7 @@
         <v>53.170999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="41">
         <v>2013</v>
       </c>
@@ -56826,7 +56826,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="41">
         <v>2014</v>
       </c>
@@ -56842,7 +56842,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="41">
         <v>2015</v>
       </c>
@@ -56856,7 +56856,7 @@
         <v>114.023</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="41">
         <v>2016</v>
       </c>
@@ -56870,7 +56870,7 @@
         <v>159.61600000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="41">
         <v>2017</v>
       </c>
@@ -56884,7 +56884,7 @@
         <v>195.67500000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="41">
         <v>2018</v>
       </c>
@@ -56898,7 +56898,7 @@
         <v>330.94499999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="41">
         <v>2019</v>
       </c>
@@ -56912,7 +56912,7 @@
         <v>319.613</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="41">
         <v>2020</v>
       </c>
@@ -56926,7 +56926,7 @@
         <v>307.589</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="41">
         <v>2021</v>
       </c>
@@ -56940,7 +56940,7 @@
         <v>607.56700000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>952</v>
       </c>
@@ -57038,7 +57038,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>953</v>
       </c>
@@ -57136,7 +57136,7 @@
         <v>11818600</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>954</v>
       </c>
@@ -57234,7 +57234,7 @@
         <v>3867</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>955</v>
       </c>
@@ -57332,7 +57332,7 @@
         <v>14375400</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>956</v>
       </c>
@@ -57430,7 +57430,7 @@
         <v>116103</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>957</v>
       </c>
@@ -57528,7 +57528,7 @@
         <v>1056400</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>958</v>
       </c>
@@ -57626,7 +57626,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>959</v>
       </c>
@@ -57724,7 +57724,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>960</v>
       </c>
@@ -57853,7 +57853,7 @@
         <v>0.43174767576613876</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>961</v>
       </c>
@@ -57982,7 +57982,7 @@
         <v>3.8591562848336439E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>962</v>
       </c>
@@ -58111,7 +58111,7 @@
         <v>0.47033923861447519</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B73" s="45"/>
       <c r="C73" s="45"/>
       <c r="D73" s="45"/>
@@ -58144,7 +58144,7 @@
       <c r="AE73" s="45"/>
       <c r="AF73" s="45"/>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>963</v>
       </c>
@@ -58180,7 +58180,7 @@
       <c r="AE74" s="45"/>
       <c r="AF74" s="45"/>
     </row>
-    <row r="76" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="F76" s="46" t="s">
         <v>971</v>
       </c>
@@ -58188,7 +58188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="F77" s="46" t="s">
         <v>972</v>
       </c>
@@ -58196,7 +58196,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="78" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="F78" s="46" t="s">
         <v>973</v>
       </c>
@@ -58205,7 +58205,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="32" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="F80" s="46" t="s">
         <v>974</v>
       </c>
@@ -58213,7 +58213,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="F81" s="46" t="s">
         <v>975</v>
       </c>
@@ -58222,7 +58222,7 @@
         <v>0.21937500000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>977</v>
       </c>
@@ -58234,42 +58234,42 @@
         <v>5.0625000000000003E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="34" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E93" s="30"/>
       <c r="F93" s="30"/>
       <c r="G93" s="30"/>
@@ -58284,7 +58284,7 @@
       <c r="N93" s="30"/>
       <c r="O93" s="30"/>
     </row>
-    <row r="94" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E94" s="29"/>
       <c r="F94" s="29"/>
       <c r="G94" s="29"/>
@@ -58297,7 +58297,7 @@
       <c r="N94" s="29"/>
       <c r="O94" s="29"/>
     </row>
-    <row r="95" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E95" s="29"/>
       <c r="F95" s="29"/>
       <c r="G95" s="29"/>
@@ -58310,7 +58310,7 @@
       <c r="N95" s="29"/>
       <c r="O95" s="29"/>
     </row>
-    <row r="96" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E96" s="29"/>
       <c r="F96" s="29"/>
       <c r="G96" s="29"/>
@@ -58325,17 +58325,17 @@
       <c r="P96" s="29"/>
       <c r="Q96" s="29"/>
     </row>
-    <row r="103" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="11:11" x14ac:dyDescent="0.25">
       <c r="K103" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>935</v>
       </c>
@@ -58344,7 +58344,7 @@
         <v>1.326343</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>936</v>
       </c>
@@ -58353,7 +58353,7 @@
         <v>1079.7512820000002</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>931</v>
       </c>
@@ -58381,18 +58381,18 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.1640625" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="18" style="7" customWidth="1"/>
-    <col min="8" max="9" width="9.1640625" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -58411,7 +58411,7 @@
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -58428,7 +58428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -58445,7 +58445,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -58462,12 +58462,12 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -58481,7 +58481,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12" t="s">
@@ -58495,7 +58495,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:38" ht="48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -58509,7 +58509,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
@@ -58651,7 +58651,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -58796,7 +58796,7 @@
         <v>0.99999998971286663</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>2</v>
       </c>
@@ -58937,7 +58937,7 @@
         <v>1.2259779596081354E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>3</v>
       </c>
@@ -59076,7 +59076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -59217,7 +59217,7 @@
         <v>3.0818463927506423E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>5</v>
       </c>
@@ -59357,7 +59357,7 @@
         <v>0.32773377328321535</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>124</v>
       </c>
@@ -59498,7 +59498,7 @@
         <v>8.6165104068937348E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23" t="s">
@@ -59641,7 +59641,7 @@
         <v>3.1168958329050089E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -59787,7 +59787,7 @@
         <v>0.9999999881542101</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>2</v>
       </c>
@@ -59927,7 +59927,7 @@
         <v>1.235369525889815E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>3</v>
       </c>
@@ -60066,7 +60066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>4</v>
       </c>
@@ -60205,7 +60205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>5</v>
       </c>
@@ -60346,7 +60346,7 @@
         <v>0.32413298494392645</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>124</v>
       </c>
@@ -60487,7 +60487,7 @@
         <v>8.6165104068937001E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23" t="s">
@@ -60630,7 +60630,7 @@
         <v>3.1136358282645159E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -60776,7 +60776,7 @@
         <v>0.9999999881542101</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>2</v>
       </c>
@@ -60917,7 +60917,7 @@
         <v>0.16005020400931197</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>3</v>
       </c>
@@ -61058,7 +61058,7 @@
         <v>0.29946959893376196</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
@@ -61197,7 +61197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>5</v>
       </c>
@@ -61338,7 +61338,7 @@
         <v>8.18920096381031E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>124</v>
       </c>
@@ -61479,7 +61479,7 @@
         <v>0.51993486392741062</v>
       </c>
     </row>
-    <row r="30" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23" t="s">
@@ -61622,7 +61622,7 @@
         <v>0.17108784051909381</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -61767,7 +61767,7 @@
         <v>0.9999999881542101</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>2</v>
       </c>
@@ -61908,7 +61908,7 @@
         <v>5.2333311909740617E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>3</v>
       </c>
@@ -62047,7 +62047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>4</v>
       </c>
@@ -62186,7 +62186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>5</v>
       </c>
@@ -62327,7 +62327,7 @@
         <v>2.7321073384308624E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>124</v>
       </c>
@@ -62468,7 +62468,7 @@
         <v>6.1785980743152003E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23" t="s">
@@ -62611,7 +62611,7 @@
         <v>6.0995164686396177E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -62756,7 +62756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>2</v>
       </c>
@@ -62895,7 +62895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>3</v>
       </c>
@@ -63034,7 +63034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>4</v>
       </c>
@@ -63173,7 +63173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>5</v>
       </c>
@@ -63312,7 +63312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>124</v>
       </c>
@@ -63451,7 +63451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23"/>
       <c r="B44" s="23"/>
       <c r="C44" s="23" t="s">
@@ -63592,7 +63592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -63737,7 +63737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>2</v>
       </c>
@@ -63876,7 +63876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>3</v>
       </c>
@@ -64015,7 +64015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>4</v>
       </c>
@@ -64154,7 +64154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>5</v>
       </c>
@@ -64293,7 +64293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>124</v>
       </c>
@@ -64432,7 +64432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="23"/>
       <c r="B51" s="23"/>
       <c r="C51" s="23" t="s">
@@ -64573,7 +64573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -64719,7 +64719,7 @@
         <v>0.99727709808185716</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>2</v>
       </c>
@@ -64858,7 +64858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>3</v>
       </c>
@@ -64997,7 +64997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>4</v>
       </c>
@@ -65137,7 +65137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>5</v>
       </c>
@@ -65276,7 +65276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>124</v>
       </c>
@@ -65415,7 +65415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23"/>
       <c r="B58" s="23"/>
       <c r="C58" s="23" t="s">
@@ -65556,7 +65556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -65701,7 +65701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>2</v>
       </c>
@@ -65840,7 +65840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>3</v>
       </c>
@@ -65979,7 +65979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>4</v>
       </c>
@@ -66118,7 +66118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>5</v>
       </c>
@@ -66257,7 +66257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>124</v>
       </c>
@@ -66396,7 +66396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23"/>
       <c r="B65" s="23"/>
       <c r="C65" s="23" t="s">
@@ -66537,7 +66537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -66682,7 +66682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>2</v>
       </c>
@@ -66821,7 +66821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>3</v>
       </c>
@@ -66960,7 +66960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>4</v>
       </c>
@@ -67099,7 +67099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>5</v>
       </c>
@@ -67238,7 +67238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>124</v>
       </c>
@@ -67377,7 +67377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23"/>
       <c r="B72" s="23"/>
       <c r="C72" s="23" t="s">
@@ -67518,7 +67518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -67663,7 +67663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>2</v>
       </c>
@@ -67802,7 +67802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>3</v>
       </c>
@@ -67941,7 +67941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>4</v>
       </c>
@@ -68080,7 +68080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>5</v>
       </c>
@@ -68219,7 +68219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>124</v>
       </c>
@@ -68358,7 +68358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="23"/>
       <c r="B79" s="23"/>
       <c r="C79" s="23" t="s">
@@ -68499,7 +68499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -68525,127 +68525,127 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:I$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,I$9))</f>
-        <v>0.10909682119561298</v>
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,I$9))</f>
+        <v>1.4774031693273055E-2</v>
       </c>
       <c r="J80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:J$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,J$9))</f>
-        <v>0.19781611144141825</v>
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,J$9))</f>
+        <v>1.984030573407751E-2</v>
       </c>
       <c r="K80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:K$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,K$9))</f>
-        <v>0.33181222783183389</v>
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,K$9))</f>
+        <v>2.6596993576865863E-2</v>
       </c>
       <c r="L80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:L$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,L$9))</f>
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,L$9))</f>
+        <v>3.5571189272636181E-2</v>
+      </c>
+      <c r="M80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,M$9))</f>
+        <v>4.7425873177566781E-2</v>
+      </c>
+      <c r="N80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,N$9))</f>
+        <v>6.2973356056996513E-2</v>
+      </c>
+      <c r="O80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,O$9))</f>
+        <v>8.317269649392238E-2</v>
+      </c>
+      <c r="P80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,P$9))</f>
+        <v>0.10909682119561293</v>
+      </c>
+      <c r="Q80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,Q$9))</f>
+        <v>0.14185106490048782</v>
+      </c>
+      <c r="R80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,R$9))</f>
+        <v>0.18242552380635635</v>
+      </c>
+      <c r="S80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,S$9))</f>
+        <v>0.23147521650098238</v>
+      </c>
+      <c r="T80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,T$9))</f>
+        <v>0.28905049737499605</v>
+      </c>
+      <c r="U80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,U$9))</f>
+        <v>0.35434369377420455</v>
+      </c>
+      <c r="V80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,V$9))</f>
+        <v>0.42555748318834102</v>
+      </c>
+      <c r="W80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,W$9))</f>
         <v>0.5</v>
       </c>
-      <c r="M80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:M$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,M$9))</f>
-        <v>0.66818777216816616</v>
-      </c>
-      <c r="N80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:N$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,N$9))</f>
-        <v>0.80218388855858169</v>
-      </c>
-      <c r="O80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:O$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,O$9))</f>
+      <c r="X80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,X$9))</f>
+        <v>0.57444251681165903</v>
+      </c>
+      <c r="Y80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,Y$9))</f>
+        <v>0.6456563062257954</v>
+      </c>
+      <c r="Z80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,Z$9))</f>
+        <v>0.71094950262500389</v>
+      </c>
+      <c r="AA80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AA$9))</f>
+        <v>0.76852478349901754</v>
+      </c>
+      <c r="AB80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AB$9))</f>
+        <v>0.81757447619364365</v>
+      </c>
+      <c r="AC80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AC$9))</f>
+        <v>0.85814893509951229</v>
+      </c>
+      <c r="AD80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AD$9))</f>
         <v>0.89090317880438707</v>
       </c>
-      <c r="P80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:P$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,P$9))</f>
-        <v>0.94267582410113127</v>
-      </c>
-      <c r="Q80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:Q$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,Q$9))</f>
-        <v>0.97068776924864364</v>
-      </c>
-      <c r="R80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:R$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,R$9))</f>
+      <c r="AE80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AE$9))</f>
+        <v>0.91682730350607766</v>
+      </c>
+      <c r="AF80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AF$9))</f>
+        <v>0.9370266439430035</v>
+      </c>
+      <c r="AG80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AG$9))</f>
+        <v>0.95257412682243336</v>
+      </c>
+      <c r="AH80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AH$9))</f>
+        <v>0.96442881072736386</v>
+      </c>
+      <c r="AI80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AI$9))</f>
+        <v>0.97340300642313404</v>
+      </c>
+      <c r="AJ80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AJ$9))</f>
+        <v>0.98015969426592253</v>
+      </c>
+      <c r="AK80">
+        <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AK$9))</f>
         <v>0.98522596830672693</v>
-      </c>
-      <c r="S80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:S$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,S$9))</f>
-        <v>0.99260845865571812</v>
-      </c>
-      <c r="T80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:T$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,T$9))</f>
-        <v>0.99631576010056411</v>
-      </c>
-      <c r="U80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:U$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,U$9))</f>
-        <v>0.99816706105750719</v>
-      </c>
-      <c r="V80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:V$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,V$9))</f>
-        <v>0.9990889488055994</v>
-      </c>
-      <c r="W80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:W$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,W$9))</f>
-        <v>0.9995473777767595</v>
-      </c>
-      <c r="X80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:X$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,X$9))</f>
-        <v>0.99977518322976666</v>
-      </c>
-      <c r="Y80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:Y$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,Y$9))</f>
-        <v>0.99988834665937043</v>
-      </c>
-      <c r="Z80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:Z$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,Z$9))</f>
-        <v>0.99994455147527717</v>
-      </c>
-      <c r="AA80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AA$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AA$9))</f>
-        <v>0.99997246430888531</v>
-      </c>
-      <c r="AB80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AB$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AB$9))</f>
-        <v>0.99998632599091541</v>
-      </c>
-      <c r="AC80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AC$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AC$9))</f>
-        <v>0.99999320964130201</v>
-      </c>
-      <c r="AD80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AD$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AD$9))</f>
-        <v>0.99999662799613631</v>
-      </c>
-      <c r="AE80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AE$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AE$9))</f>
-        <v>0.99999832550959444</v>
-      </c>
-      <c r="AF80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AF$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AF$9))</f>
-        <v>0.99999916847197223</v>
-      </c>
-      <c r="AG80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AG$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AG$9))</f>
-        <v>0.99999958707522896</v>
-      </c>
-      <c r="AH80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AH$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AH$9))</f>
-        <v>0.99999979494758462</v>
-      </c>
-      <c r="AI80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AI$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AI$9))</f>
-        <v>0.99999989817397339</v>
-      </c>
-      <c r="AJ80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AJ$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AJ$9))</f>
-        <v>0.99999994943468906</v>
-      </c>
-      <c r="AK80">
-        <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AK$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AK$9))</f>
-        <v>0.99999997489000902</v>
       </c>
       <c r="AL80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$O$2/(1+EXP($O$3*(COUNT($H$9:AL$9)+$O$4))),TREND($D80:$E80,$D$9:$E$9,AL$9))</f>
         <v>0.99999998753074737</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
         <v>2</v>
       </c>
@@ -68785,7 +68785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C82" t="s">
         <v>3</v>
       </c>
@@ -68924,7 +68924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>4</v>
       </c>
@@ -69064,7 +69064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C84" t="s">
         <v>5</v>
       </c>
@@ -69204,7 +69204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C85" t="s">
         <v>124</v>
       </c>
@@ -69344,7 +69344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23"/>
       <c r="B86" s="23"/>
       <c r="C86" s="23" t="s">
@@ -69486,7 +69486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -69631,7 +69631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>2</v>
       </c>
@@ -69770,7 +69770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>3</v>
       </c>
@@ -69909,7 +69909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
         <v>4</v>
       </c>
@@ -70048,7 +70048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>5</v>
       </c>
@@ -70187,7 +70187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C92" t="s">
         <v>124</v>
       </c>
@@ -70326,7 +70326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="23"/>
       <c r="B93" s="23"/>
       <c r="C93" s="23" t="s">
